--- a/胎壓偵測/DS_Data.xlsx
+++ b/胎壓偵測/DS_Data.xlsx
@@ -6703,10 +6703,26 @@
           <t>ATP</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>02/2014 -, 06/2011 - 01/2014</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Gen 4 3000, HS 3002 |  &lt; 3.6 Bar Reifendruck, RTPMS 3281</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>SCHRADER</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
